--- a/logs/test_results_sample.xlsx
+++ b/logs/test_results_sample.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>No salary data available for Sep 2025.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,11 +506,7 @@
           <t>get_salary</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Sep-2025</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -545,14 +541,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>get_salary</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sep-2025</t>
-        </is>
-      </c>
+          <t>analyze_salary</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,14 +579,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>get_salary</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sep-2025</t>
-        </is>
-      </c>
+          <t>analyze_salary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -614,7 +602,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>Salary data for the selected period is not available yet. Please check back later or contact payroll.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -629,14 +617,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>get_salary</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sep-2025</t>
-        </is>
-      </c>
+          <t>analyze_salary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -671,14 +655,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>get_salary</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Apr-2025</t>
-        </is>
-      </c>
+          <t>analyze_salary</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -698,7 +678,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>No OT/allowance data available for May 2025.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -713,14 +693,10 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>get_salary</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>May-2025</t>
-        </is>
-      </c>
+          <t>get_ot</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -740,7 +716,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>No OT/allowance data available for May 2025.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -755,14 +731,10 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>get_salary</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>May-2025</t>
-        </is>
-      </c>
+          <t>get_ot</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -782,7 +754,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>No tax data available for May 2025.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -800,11 +772,7 @@
           <t>get_tax</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>May-2025</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -824,7 +792,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>No salary data available for Mar 2025.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -872,10 +840,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>faq</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>payroll</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>get_salary</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -930,12 +902,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>Tax regime once selected during a financial year cannot be changed until the end of the financial year.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1013,7 +985,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>get_salary</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1051,7 +1023,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>get_salary</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1074,7 +1046,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>No salary data available for Jun 2025.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1089,14 +1061,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Jun-2025</t>
-        </is>
-      </c>
+          <t>get_salary</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1116,12 +1084,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>Based on the tool data, your net taxable income for January 2026 is:
+$305,563 (total tax liability)
+Please note that this information is based solely on the provided tool data and may not reflect any additional factors or calculations that might be relevant to determining your actual net taxable income.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1134,11 +1104,7 @@
           <t>get_tax</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Jan-2026</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1158,12 +1124,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>According to the tool data, your total gross salary for January 2026 is $20,418.7.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1176,11 +1142,7 @@
           <t>get_salary</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Jan-2026</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1200,12 +1162,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>According to the tool data, your surcharge on income tax for January 2026 is not explicitly stated. However, we can infer that there is no surcharge since the total tax liability is provided without any additional information indicating a surcharge.
+So, my answer would be: There is no surcharge on income tax for January 2026.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1218,11 +1181,7 @@
           <t>get_tax</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Jan-2026</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1242,12 +1201,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>I could not confidently answer that. Please contact the payroll team.</t>
+          <t>According to the tool data, your total tax liability for January 2026 is $305,563.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1260,11 +1219,7 @@
           <t>get_tax</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Jan-2026</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
